--- a/artfynd/A 58054-2019 artfynd.xlsx
+++ b/artfynd/A 58054-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127148067</v>
       </c>
       <c r="B3" t="n">
-        <v>79059</v>
+        <v>79090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127148036</v>
       </c>
       <c r="B7" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127148059</v>
       </c>
       <c r="B8" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127148033</v>
+        <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718773</v>
+        <v>718694</v>
       </c>
       <c r="R9" t="n">
-        <v>7284302</v>
+        <v>7284325</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127148038</v>
+        <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718694</v>
+        <v>718773</v>
       </c>
       <c r="R10" t="n">
-        <v>7284325</v>
+        <v>7284302</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148068</v>
+        <v>127148051</v>
       </c>
       <c r="B12" t="n">
-        <v>78386</v>
+        <v>78678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718777</v>
+        <v>718726</v>
       </c>
       <c r="R12" t="n">
-        <v>7284375</v>
+        <v>7284409</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B13" t="n">
-        <v>78647</v>
+        <v>78417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R13" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,7 +1855,7 @@
         <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127148046</v>
       </c>
       <c r="B15" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148045</v>
+        <v>127148062</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>92609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718709</v>
+        <v>718734</v>
       </c>
       <c r="R16" t="n">
-        <v>7284346</v>
+        <v>7284278</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148062</v>
+        <v>127148031</v>
       </c>
       <c r="B17" t="n">
-        <v>92535</v>
+        <v>79090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718734</v>
+        <v>718770</v>
       </c>
       <c r="R17" t="n">
-        <v>7284278</v>
+        <v>7284311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2222,6 +2222,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2240,32 +2241,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148031</v>
+        <v>127148045</v>
       </c>
       <c r="B18" t="n">
-        <v>79059</v>
+        <v>80142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2275,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718770</v>
+        <v>718709</v>
       </c>
       <c r="R18" t="n">
-        <v>7284311</v>
+        <v>7284346</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,7 +2320,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>127148042</v>
       </c>
       <c r="B19" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148065</v>
+        <v>127148054</v>
       </c>
       <c r="B20" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718669</v>
+        <v>718747</v>
       </c>
       <c r="R20" t="n">
-        <v>7284342</v>
+        <v>7284415</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,32 +2532,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148021</v>
+        <v>127148065</v>
       </c>
       <c r="B21" t="n">
-        <v>79598</v>
+        <v>92609</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718756</v>
+        <v>718669</v>
       </c>
       <c r="R21" t="n">
-        <v>7284289</v>
+        <v>7284342</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2632,7 +2632,7 @@
         <v>127148034</v>
       </c>
       <c r="B22" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148054</v>
+        <v>127148021</v>
       </c>
       <c r="B23" t="n">
-        <v>92535</v>
+        <v>79629</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718747</v>
+        <v>718756</v>
       </c>
       <c r="R23" t="n">
-        <v>7284415</v>
+        <v>7284289</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2826,7 +2826,7 @@
         <v>127148058</v>
       </c>
       <c r="B24" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148057</v>
       </c>
       <c r="B25" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127148060</v>
+        <v>127148064</v>
       </c>
       <c r="B26" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718731</v>
+        <v>718686</v>
       </c>
       <c r="R26" t="n">
-        <v>7284349</v>
+        <v>7284325</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127148064</v>
+        <v>127148060</v>
       </c>
       <c r="B27" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718686</v>
+        <v>718731</v>
       </c>
       <c r="R27" t="n">
-        <v>7284325</v>
+        <v>7284349</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148043</v>
+        <v>127148061</v>
       </c>
       <c r="B30" t="n">
-        <v>97245</v>
+        <v>92609</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718667</v>
+        <v>718771</v>
       </c>
       <c r="R30" t="n">
-        <v>7284313</v>
+        <v>7284306</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,32 +3502,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148061</v>
+        <v>127148020</v>
       </c>
       <c r="B31" t="n">
-        <v>92535</v>
+        <v>79629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718771</v>
+        <v>718765</v>
       </c>
       <c r="R31" t="n">
-        <v>7284306</v>
+        <v>7284389</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,32 +3599,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148020</v>
+        <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>79598</v>
+        <v>97320</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718765</v>
+        <v>718667</v>
       </c>
       <c r="R32" t="n">
-        <v>7284389</v>
+        <v>7284313</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3699,7 +3699,7 @@
         <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
